--- a/backend/data/financials_by_company/1402.HK.xlsx
+++ b/backend/data/financials_by_company/1402.HK.xlsx
@@ -3960,7 +3960,7 @@
         <v>-1056000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>2.245</v>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA2" t="n">
         <v>-0.026300013</v>
